--- a/34th_Backgammon-championships_3c_output.xlsx
+++ b/34th_Backgammon-championships_3c_output.xlsx
@@ -1321,7 +1321,7 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
         <v>6</v>
@@ -1336,7 +1336,7 @@
         <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
         <v>4</v>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
@@ -1501,7 +1501,7 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>9</v>
@@ -1623,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
